--- a/import-templates/product-import-template.xlsx
+++ b/import-templates/product-import-template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Products" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Products'!$A$1:$AG$1</definedName>
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,15 @@
     </font>
     <font>
       <color rgb="0060736E"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00075B40"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="0060736E"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="000000FF"/>
@@ -137,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -172,6 +181,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -190,16 +203,16 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -285,181 +298,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>CREATE, UPDATE, or UPSERT. UPSERT is the safest default for a reusable file.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Groups variants into one product. Repeat the same handle for multiple SKUs.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Customer-facing English product name.</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional lowercase URL slug using letters, numbers, and hyphens.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Recommended maximum 180 characters for catalog cards.</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Full English description. Include package, storage, ingredients, and serving information as applicable.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Category hierarchy such as Snacks &gt; Fruit. The importer may create missing categories only when that option is explicitly enabled.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Sellable option such as 8 oz bag or 20 count.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Unique stock keeping unit. Case-insensitive uniqueness is enforced.</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional UPC/EAN/GTIN. Must be unique when present.</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional JSON object, for example {"size":"8 oz","flavor":"mango"}.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Retail price in USD, 0 or greater.</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional wholesale price in USD. Wholesale pricing does not automatically make the customer tax exempt.</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Current unit cost in USD, 0 or greater.</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>TRUE or FALSE.</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t>Opening on-hand quantity. Use only when creating a new SKU; later changes should use inventory movements.</t>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
-      <text>
-        <t>Low-stock threshold, 0 or greater.</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <t>Inventory location code, for example MAIN.</t>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t>TRUE or FALSE. Final tax treatment also depends on customer and jurisdiction.</t>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
-      <text>
-        <t>Each, bag, box, case, bottle, jar, pack, pound, ounce, or custom unit.</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional shipping weight in ounces.</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t>TRUE or FALSE. Use FALSE to import as inactive/draft.</t>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 1. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 2. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 3. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 4. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 5. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 6. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 7. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 8. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 9. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="AF1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional image URL 10. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
-      <text>
-        <t>Optional existing video URL. For new uploads, use Cloudflare Stream through the admin UI.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -751,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -767,7 +605,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bright Basket Foods — Product Import Template</t>
+          <t>Vinameals — Product Import Template</t>
         </is>
       </c>
     </row>
@@ -984,25 +822,462 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Field guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>operation</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>CREATE, UPDATE, or UPSERT. UPSERT is the safest default for a reusable file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>product_handle</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Groups variants into one product. Repeat the same handle for multiple SKUs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Customer-facing English product name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Optional lowercase URL slug using letters, numbers, and hyphens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>short_description</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Recommended maximum 180 characters for catalog cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Full English description. Include package, storage, ingredients, and serving information as applicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>category_path</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Category hierarchy such as Snacks &gt; Fruit. The importer may create missing categories only when that option is explicitly enabled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>variant_name</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Sellable option such as 8 oz bag or 20 count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Unique stock keeping unit. Case-insensitive uniqueness is enforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Optional UPC/EAN/GTIN. Must be unique when present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>attributes_json</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Optional JSON object, for example {"size":"8 oz","flavor":"mango"}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>retail_price</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Retail price in USD, 0 or greater.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>wholesale_price</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Optional wholesale price in USD. Wholesale pricing does not automatically make the customer tax exempt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>cost_price</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Current unit cost in USD, 0 or greater.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>track_inventory</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>TRUE or FALSE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>opening_quantity</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Opening on-hand quantity. Use only when creating a new SKU; later changes should use inventory movements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>reorder_point</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Low-stock threshold, 0 or greater.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>location_code</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Inventory location code, for example MAIN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>taxable</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>TRUE or FALSE. Final tax treatment also depends on customer and jurisdiction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Each, bag, box, case, bottle, jar, pack, pound, ounce, or custom unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>weight_oz</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Optional shipping weight in ounces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>TRUE or FALSE. Use FALSE to import as inactive/draft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>image_url_1</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 1. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>image_url_2</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 2. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>image_url_3</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 3. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>image_url_4</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 4. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>image_url_5</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 5. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>image_url_6</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 6. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>image_url_7</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 7. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>image_url_8</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 8. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>image_url_9</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 9. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>image_url_10</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>Optional image URL 10. A product may have no more than 10 images. image_url_1 becomes the cover image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>video_url</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>Optional existing video URL. For new uploads, use Cloudflare Stream through the admin UI.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="51">
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="A5:H6"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B46:H46"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B13:H13"/>
     <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B42:H42"/>
     <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A5:H6"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="B60:H60"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1053,606 +1328,606 @@
   </cols>
   <sheetData>
     <row r="1" ht="52" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>operation</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>product_handle</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>slug</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>short_description</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>category_path</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>variant_name</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>barcode</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>attributes_json</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="L1" s="19" t="inlineStr">
         <is>
           <t>retail_price</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="M1" s="19" t="inlineStr">
         <is>
           <t>wholesale_price</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="N1" s="19" t="inlineStr">
         <is>
           <t>cost_price</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="O1" s="20" t="inlineStr">
         <is>
           <t>track_inventory</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="P1" s="20" t="inlineStr">
         <is>
           <t>opening_quantity</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="Q1" s="20" t="inlineStr">
         <is>
           <t>reorder_point</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="R1" s="20" t="inlineStr">
         <is>
           <t>location_code</t>
         </is>
       </c>
-      <c r="S1" s="19" t="inlineStr">
+      <c r="S1" s="21" t="inlineStr">
         <is>
           <t>taxable</t>
         </is>
       </c>
-      <c r="T1" s="19" t="inlineStr">
+      <c r="T1" s="21" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="U1" s="19" t="inlineStr">
+      <c r="U1" s="21" t="inlineStr">
         <is>
           <t>weight_oz</t>
         </is>
       </c>
-      <c r="V1" s="19" t="inlineStr">
+      <c r="V1" s="21" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" s="14" t="inlineStr">
+      <c r="W1" s="16" t="inlineStr">
         <is>
           <t>image_url_1</t>
         </is>
       </c>
-      <c r="X1" s="14" t="inlineStr">
+      <c r="X1" s="16" t="inlineStr">
         <is>
           <t>image_url_2</t>
         </is>
       </c>
-      <c r="Y1" s="14" t="inlineStr">
+      <c r="Y1" s="16" t="inlineStr">
         <is>
           <t>image_url_3</t>
         </is>
       </c>
-      <c r="Z1" s="14" t="inlineStr">
+      <c r="Z1" s="16" t="inlineStr">
         <is>
           <t>image_url_4</t>
         </is>
       </c>
-      <c r="AA1" s="14" t="inlineStr">
+      <c r="AA1" s="16" t="inlineStr">
         <is>
           <t>image_url_5</t>
         </is>
       </c>
-      <c r="AB1" s="14" t="inlineStr">
+      <c r="AB1" s="16" t="inlineStr">
         <is>
           <t>image_url_6</t>
         </is>
       </c>
-      <c r="AC1" s="14" t="inlineStr">
+      <c r="AC1" s="16" t="inlineStr">
         <is>
           <t>image_url_7</t>
         </is>
       </c>
-      <c r="AD1" s="14" t="inlineStr">
+      <c r="AD1" s="16" t="inlineStr">
         <is>
           <t>image_url_8</t>
         </is>
       </c>
-      <c r="AE1" s="14" t="inlineStr">
+      <c r="AE1" s="16" t="inlineStr">
         <is>
           <t>image_url_9</t>
         </is>
       </c>
-      <c r="AF1" s="14" t="inlineStr">
+      <c r="AF1" s="16" t="inlineStr">
         <is>
           <t>image_url_10</t>
         </is>
       </c>
-      <c r="AG1" s="14" t="inlineStr">
+      <c r="AG1" s="16" t="inlineStr">
         <is>
           <t>video_url</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>UPSERT</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>tropical-mango-slices</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>Tropical Mango Slices</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>tropical-mango-slices</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>Sweet, sunny mango slices ready to enjoy.</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>Bright tropical mango slices with a soft bite and naturally sweet flavor.</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>Snacks &gt; Fruit</t>
         </is>
       </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>8 oz bag</t>
         </is>
       </c>
-      <c r="I2" s="20" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>MANGO-8OZ</t>
         </is>
       </c>
-      <c r="J2" s="20" t="inlineStr"/>
-      <c r="K2" s="21" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr"/>
+      <c r="K2" s="23" t="inlineStr">
         <is>
           <t>{"size":"8 oz"}</t>
         </is>
       </c>
-      <c r="L2" s="22" t="n">
+      <c r="L2" s="24" t="n">
         <v>8.99</v>
       </c>
-      <c r="M2" s="22" t="n">
+      <c r="M2" s="24" t="n">
         <v>6.25</v>
       </c>
-      <c r="N2" s="22" t="n">
+      <c r="N2" s="24" t="n">
         <v>3.4</v>
       </c>
-      <c r="O2" s="20" t="b">
+      <c r="O2" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="23" t="n">
+      <c r="P2" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="Q2" s="23" t="n">
+      <c r="Q2" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="R2" s="20" t="inlineStr">
+      <c r="R2" s="22" t="inlineStr">
         <is>
           <t>MAIN</t>
         </is>
       </c>
-      <c r="S2" s="20" t="b">
+      <c r="S2" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="T2" s="20" t="inlineStr">
+      <c r="T2" s="22" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="U2" s="23" t="n">
+      <c r="U2" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="V2" s="20" t="b">
+      <c r="V2" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="W2" s="20" t="inlineStr">
+      <c r="W2" s="22" t="inlineStr">
         <is>
           <t>https://media.example.com/products/mango-1.webp</t>
         </is>
       </c>
-      <c r="X2" s="20" t="inlineStr">
+      <c r="X2" s="22" t="inlineStr">
         <is>
           <t>https://media.example.com/products/mango-2.webp</t>
         </is>
       </c>
-      <c r="Y2" s="20" t="inlineStr"/>
-      <c r="Z2" s="20" t="inlineStr"/>
-      <c r="AA2" s="20" t="inlineStr"/>
-      <c r="AB2" s="20" t="inlineStr"/>
-      <c r="AC2" s="20" t="inlineStr"/>
-      <c r="AD2" s="20" t="inlineStr"/>
-      <c r="AE2" s="20" t="inlineStr"/>
-      <c r="AF2" s="20" t="inlineStr"/>
-      <c r="AG2" s="20" t="inlineStr"/>
+      <c r="Y2" s="22" t="inlineStr"/>
+      <c r="Z2" s="22" t="inlineStr"/>
+      <c r="AA2" s="22" t="inlineStr"/>
+      <c r="AB2" s="22" t="inlineStr"/>
+      <c r="AC2" s="22" t="inlineStr"/>
+      <c r="AD2" s="22" t="inlineStr"/>
+      <c r="AE2" s="22" t="inlineStr"/>
+      <c r="AF2" s="22" t="inlineStr"/>
+      <c r="AG2" s="22" t="inlineStr"/>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>UPSERT</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>garden-veggie-dumplings</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Garden Veggie Dumplings</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>garden-veggie-dumplings</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>Tender dumplings filled with colorful vegetables.</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>Freezer-friendly vegetable dumplings for quick lunches and family meals.</t>
         </is>
       </c>
-      <c r="G3" s="20" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t>Frozen &gt; Dumplings</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>20 count</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>DUMP-VEG-20</t>
         </is>
       </c>
-      <c r="J3" s="20" t="inlineStr"/>
-      <c r="K3" s="21" t="inlineStr">
+      <c r="J3" s="22" t="inlineStr"/>
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>{"count":20}</t>
         </is>
       </c>
-      <c r="L3" s="22" t="n">
+      <c r="L3" s="24" t="n">
         <v>12.99</v>
       </c>
-      <c r="M3" s="22" t="n">
+      <c r="M3" s="24" t="n">
         <v>9.4</v>
       </c>
-      <c r="N3" s="22" t="n">
+      <c r="N3" s="24" t="n">
         <v>5.2</v>
       </c>
-      <c r="O3" s="20" t="b">
+      <c r="O3" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="P3" s="23" t="n">
+      <c r="P3" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="Q3" s="23" t="n">
+      <c r="Q3" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="R3" s="20" t="inlineStr">
+      <c r="R3" s="22" t="inlineStr">
         <is>
           <t>MAIN</t>
         </is>
       </c>
-      <c r="S3" s="20" t="b">
+      <c r="S3" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="T3" s="20" t="inlineStr">
+      <c r="T3" s="22" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="U3" s="23" t="n">
+      <c r="U3" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="V3" s="20" t="b">
+      <c r="V3" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="W3" s="20" t="inlineStr">
+      <c r="W3" s="22" t="inlineStr">
         <is>
           <t>https://media.example.com/products/dumplings-1.webp</t>
         </is>
       </c>
-      <c r="X3" s="20" t="inlineStr"/>
-      <c r="Y3" s="20" t="inlineStr"/>
-      <c r="Z3" s="20" t="inlineStr"/>
-      <c r="AA3" s="20" t="inlineStr"/>
-      <c r="AB3" s="20" t="inlineStr"/>
-      <c r="AC3" s="20" t="inlineStr"/>
-      <c r="AD3" s="20" t="inlineStr"/>
-      <c r="AE3" s="20" t="inlineStr"/>
-      <c r="AF3" s="20" t="inlineStr"/>
-      <c r="AG3" s="20" t="inlineStr"/>
+      <c r="X3" s="22" t="inlineStr"/>
+      <c r="Y3" s="22" t="inlineStr"/>
+      <c r="Z3" s="22" t="inlineStr"/>
+      <c r="AA3" s="22" t="inlineStr"/>
+      <c r="AB3" s="22" t="inlineStr"/>
+      <c r="AC3" s="22" t="inlineStr"/>
+      <c r="AD3" s="22" t="inlineStr"/>
+      <c r="AE3" s="22" t="inlineStr"/>
+      <c r="AF3" s="22" t="inlineStr"/>
+      <c r="AG3" s="22" t="inlineStr"/>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>UPSERT</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>golden-chili-crisp</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>Golden Chili Crisp</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>golden-chili-crisp</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Crunchy, savory, and gently spicy.</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>A spoonable chili crisp for noodles, rice, eggs, and vegetables.</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="G4" s="22" t="inlineStr">
         <is>
           <t>Sauces &gt; Chili</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>6 oz jar</t>
         </is>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>CHILI-6OZ</t>
         </is>
       </c>
-      <c r="J4" s="20" t="inlineStr"/>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="J4" s="22" t="inlineStr"/>
+      <c r="K4" s="23" t="inlineStr">
         <is>
           <t>{"size":"6 oz"}</t>
         </is>
       </c>
-      <c r="L4" s="22" t="n">
+      <c r="L4" s="24" t="n">
         <v>10.5</v>
       </c>
-      <c r="M4" s="22" t="n">
+      <c r="M4" s="24" t="n">
         <v>7.6</v>
       </c>
-      <c r="N4" s="22" t="n">
+      <c r="N4" s="24" t="n">
         <v>3.85</v>
       </c>
-      <c r="O4" s="20" t="b">
+      <c r="O4" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="P4" s="23" t="n">
+      <c r="P4" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="Q4" s="23" t="n">
+      <c r="Q4" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="R4" s="20" t="inlineStr">
+      <c r="R4" s="22" t="inlineStr">
         <is>
           <t>MAIN</t>
         </is>
       </c>
-      <c r="S4" s="20" t="b">
+      <c r="S4" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="T4" s="20" t="inlineStr">
+      <c r="T4" s="22" t="inlineStr">
         <is>
           <t>jar</t>
         </is>
       </c>
-      <c r="U4" s="23" t="n">
+      <c r="U4" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="V4" s="20" t="b">
+      <c r="V4" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="W4" s="20" t="inlineStr">
+      <c r="W4" s="22" t="inlineStr">
         <is>
           <t>https://media.example.com/products/chili-1.webp</t>
         </is>
       </c>
-      <c r="X4" s="20" t="inlineStr"/>
-      <c r="Y4" s="20" t="inlineStr"/>
-      <c r="Z4" s="20" t="inlineStr"/>
-      <c r="AA4" s="20" t="inlineStr"/>
-      <c r="AB4" s="20" t="inlineStr"/>
-      <c r="AC4" s="20" t="inlineStr"/>
-      <c r="AD4" s="20" t="inlineStr"/>
-      <c r="AE4" s="20" t="inlineStr"/>
-      <c r="AF4" s="20" t="inlineStr"/>
-      <c r="AG4" s="20" t="inlineStr"/>
+      <c r="X4" s="22" t="inlineStr"/>
+      <c r="Y4" s="22" t="inlineStr"/>
+      <c r="Z4" s="22" t="inlineStr"/>
+      <c r="AA4" s="22" t="inlineStr"/>
+      <c r="AB4" s="22" t="inlineStr"/>
+      <c r="AC4" s="22" t="inlineStr"/>
+      <c r="AD4" s="22" t="inlineStr"/>
+      <c r="AE4" s="22" t="inlineStr"/>
+      <c r="AF4" s="22" t="inlineStr"/>
+      <c r="AG4" s="22" t="inlineStr"/>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>UPSERT</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>pure-coconut-water</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Pure Coconut Water</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>pure-coconut-water</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Clean, refreshing coconut water.</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Serve chilled for a crisp and refreshing drink.</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>Beverages &gt; Coconut Water</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>16.9 fl oz bottle</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>COCO-169</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr"/>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr"/>
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>{"volume":"16.9 fl oz"}</t>
         </is>
       </c>
-      <c r="L5" s="22" t="n">
+      <c r="L5" s="24" t="n">
         <v>3.99</v>
       </c>
-      <c r="M5" s="22" t="n">
+      <c r="M5" s="24" t="n">
         <v>2.65</v>
       </c>
-      <c r="N5" s="22" t="n">
+      <c r="N5" s="24" t="n">
         <v>1.35</v>
       </c>
-      <c r="O5" s="20" t="b">
+      <c r="O5" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="P5" s="23" t="n">
+      <c r="P5" s="25" t="n">
         <v>64</v>
       </c>
-      <c r="Q5" s="23" t="n">
+      <c r="Q5" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="R5" s="20" t="inlineStr">
+      <c r="R5" s="22" t="inlineStr">
         <is>
           <t>MAIN</t>
         </is>
       </c>
-      <c r="S5" s="20" t="b">
+      <c r="S5" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="T5" s="20" t="inlineStr">
+      <c r="T5" s="22" t="inlineStr">
         <is>
           <t>bottle</t>
         </is>
       </c>
-      <c r="U5" s="23" t="n">
+      <c r="U5" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="V5" s="20" t="b">
+      <c r="V5" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="W5" s="20" t="inlineStr">
+      <c r="W5" s="22" t="inlineStr">
         <is>
           <t>https://media.example.com/products/coconut-1.webp</t>
         </is>
       </c>
-      <c r="X5" s="20" t="inlineStr"/>
-      <c r="Y5" s="20" t="inlineStr"/>
-      <c r="Z5" s="20" t="inlineStr"/>
-      <c r="AA5" s="20" t="inlineStr"/>
-      <c r="AB5" s="20" t="inlineStr"/>
-      <c r="AC5" s="20" t="inlineStr"/>
-      <c r="AD5" s="20" t="inlineStr"/>
-      <c r="AE5" s="20" t="inlineStr"/>
-      <c r="AF5" s="20" t="inlineStr"/>
-      <c r="AG5" s="20" t="inlineStr"/>
+      <c r="X5" s="22" t="inlineStr"/>
+      <c r="Y5" s="22" t="inlineStr"/>
+      <c r="Z5" s="22" t="inlineStr"/>
+      <c r="AA5" s="22" t="inlineStr"/>
+      <c r="AB5" s="22" t="inlineStr"/>
+      <c r="AC5" s="22" t="inlineStr"/>
+      <c r="AD5" s="22" t="inlineStr"/>
+      <c r="AE5" s="22" t="inlineStr"/>
+      <c r="AF5" s="22" t="inlineStr"/>
+      <c r="AG5" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AG1"/>
-  <conditionalFormatting sqref="L2:L2000">
+  <conditionalFormatting sqref="B2:B2000">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND($B2&lt;&gt;"",L2="")</formula>
+      <formula>AND($B2&lt;&gt;"",B2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A2000">
+  <conditionalFormatting sqref="N2:N2000">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>AND($B2&lt;&gt;"",A2="")</formula>
+      <formula>AND($B2&lt;&gt;"",N2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I2000">
@@ -1660,19 +1935,19 @@
       <formula>AND($B2&lt;&gt;"",I2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N2000">
+  <conditionalFormatting sqref="L2:L2000">
     <cfRule type="expression" priority="4" dxfId="0">
-      <formula>AND($B2&lt;&gt;"",N2="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B2000">
-    <cfRule type="expression" priority="5" dxfId="0">
-      <formula>AND($B2&lt;&gt;"",B2="")</formula>
+      <formula>AND($B2&lt;&gt;"",L2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C2000">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>AND($B2&lt;&gt;"",C2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A2000">
     <cfRule type="expression" priority="6" dxfId="0">
-      <formula>AND($B2&lt;&gt;"",C2="")</formula>
+      <formula>AND($B2&lt;&gt;"",A2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
@@ -1699,7 +1974,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/import-templates/product-import-template.xlsx
+++ b/import-templates/product-import-template.xlsx
@@ -12,27 +12,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Vinameals — Simple product import</t>
   </si>
   <si>
-    <t>Only 3 columns required on the Products sheet:</t>
-  </si>
-  <si>
-    <t>product_name | retail_price | inventory</t>
-  </si>
-  <si>
-    <t>Each row creates one product with auto ID, handle, and SKU.</t>
-  </si>
-  <si>
-    <t>No category → product only appears under Shop all until you assign a category.</t>
-  </si>
-  <si>
-    <t>Images and video: upload later in Admin → Products.</t>
-  </si>
-  <si>
-    <t>Optional columns (if present): sale_price, cost_price, sku, short_description, status</t>
+    <t>How to fill</t>
+  </si>
+  <si>
+    <t>Use the Products sheet. Headers are on ONE horizontal row. Each product is ONE horizontal data row under the headers.</t>
+  </si>
+  <si>
+    <t>Required columns (left → right on Products sheet)</t>
   </si>
   <si>
     <t>product_name</t>
@@ -44,10 +35,28 @@
     <t>inventory</t>
   </si>
   <si>
+    <t>Tên sản phẩm</t>
+  </si>
+  <si>
+    <t>Giá bán (USD)</t>
+  </si>
+  <si>
+    <t>Số lượng tồn</t>
+  </si>
+  <si>
+    <t>Example (same layout as Products sheet)</t>
+  </si>
+  <si>
     <t>Tropical Mango Slices</t>
   </si>
   <si>
     <t>Garden Veggie Dumplings</t>
+  </si>
+  <si>
+    <t>Do NOT list fields vertically (one field per row). Always use columns across the top, products down the rows.</t>
+  </si>
+  <si>
+    <t>Auto-created: product ID, handle, slug, SKU. No category → only Shop all. Images later in Admin.</t>
   </si>
   <si>
     <t>Golden Chili Crisp</t>
@@ -57,7 +66,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -67,18 +76,41 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF075B40"/>
       <sz val="16"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFB42318"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF7E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B7A55"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -93,10 +125,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,45 +482,119 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>8.99</v>
+      </c>
+      <c r="C12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>12.99</v>
+      </c>
+      <c r="C13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A17:C17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -485,27 +605,27 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>9</v>
+    <row r="1" ht="22" customHeight="1" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2">
+        <v>11</v>
+      </c>
+      <c r="B2" s="10">
         <v>8.99</v>
       </c>
       <c r="C2">
@@ -514,9 +634,9 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="B3" s="10">
         <v>12.99</v>
       </c>
       <c r="C3">
@@ -525,9 +645,9 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="B4" s="10">
         <v>10.5</v>
       </c>
       <c r="C4">
@@ -535,6 +655,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
